--- a/data/trending_integrated_20260909_13.xlsx
+++ b/data/trending_integrated_20260909_13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F2" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G2" t="n">
-        <v>1306</v>
+        <v>1346</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29616866855</v>
+        <v>29638325495</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -676,7 +676,7 @@
         <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="H3" t="n">
         <v>2.46</v>
@@ -702,7 +702,7 @@
         <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>37705364175</v>
+        <v>37761774195</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -711,7 +711,7 @@
         <v>1206</v>
       </c>
       <c r="R3" t="n">
-        <v>29000</v>
+        <v>34000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12340</v>
+        <v>2640</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+23.03%</t>
+          <t>+22.22%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.08</v>
+        <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="G4" t="n">
-        <v>279</v>
+        <v>147</v>
       </c>
       <c r="H4" t="n">
-        <v>0.36</v>
+        <v>5.26</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>10030</v>
+        <v>2160</v>
       </c>
       <c r="K4" t="n">
-        <v>10270</v>
+        <v>2200</v>
       </c>
       <c r="L4" t="n">
-        <v>12790</v>
+        <v>2670</v>
       </c>
       <c r="M4" t="n">
-        <v>10040</v>
+        <v>2200</v>
       </c>
       <c r="N4" t="n">
-        <v>0.44</v>
+        <v>5.49</v>
       </c>
       <c r="O4" t="n">
-        <v>177479462045</v>
+        <v>27353186547</v>
       </c>
       <c r="P4" t="n">
-        <v>20850</v>
+        <v>2670</v>
       </c>
       <c r="Q4" t="n">
-        <v>4020</v>
+        <v>1418</v>
       </c>
       <c r="R4" t="n">
-        <v>25000</v>
+        <v>-166000</v>
       </c>
       <c r="S4" t="n">
-        <v>19000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 SMR 및 가스터빈 발전소 관련 뉴스, 품절주·주포 움직임 주목.</t>
+          <t>경영권 분쟁 및 신규 대주주 관련 긍정적 전망. 단기 급등 기대감 및 기타법인 매수세 유입 관찰. 과열 우려 및 매도량 급증 주의.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['SMR', '가스터빈', '품절주']</t>
+          <t>['경영권분쟁', '기타법인', '단기과열']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13770</v>
+        <v>12210</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+16.60%</t>
+          <t>+21.73%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.22</v>
+        <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="F5" t="n">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="G5" t="n">
-        <v>1184</v>
+        <v>312</v>
       </c>
       <c r="H5" t="n">
-        <v>5.64</v>
+        <v>0.36</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>11810</v>
+        <v>10030</v>
       </c>
       <c r="K5" t="n">
-        <v>12050</v>
+        <v>10270</v>
       </c>
       <c r="L5" t="n">
-        <v>14550</v>
+        <v>12790</v>
       </c>
       <c r="M5" t="n">
-        <v>11950</v>
+        <v>10040</v>
       </c>
       <c r="N5" t="n">
-        <v>5.42</v>
+        <v>0.44</v>
       </c>
       <c r="O5" t="n">
-        <v>439506685865</v>
+        <v>184430443710</v>
       </c>
       <c r="P5" t="n">
-        <v>30200</v>
+        <v>20850</v>
       </c>
       <c r="Q5" t="n">
-        <v>3540</v>
+        <v>4020</v>
       </c>
       <c r="R5" t="n">
-        <v>515000</v>
+        <v>4000</v>
       </c>
       <c r="S5" t="n">
-        <v>18000</v>
+        <v>19000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>체코·미국 원전 사업 및 사우디 등 해외 수주 기대감. 정부 정책 수혜.</t>
+          <t>가스터빈 및 원전 관련 사업 부각. 국내 1위 업체로 미국 시장 진출 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전', '수주', '해외']</t>
+          <t>['가스터빈', '원전', '미국 시장']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>현대바이오</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7210</v>
+        <v>13870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+15.18%</t>
+          <t>+17.44%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="E6" t="n">
-        <v>181</v>
+        <v>248</v>
       </c>
       <c r="F6" t="n">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="G6" t="n">
-        <v>944</v>
+        <v>1252</v>
       </c>
       <c r="H6" t="n">
-        <v>7.4</v>
+        <v>5.64</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6260</v>
+        <v>11810</v>
       </c>
       <c r="K6" t="n">
-        <v>6200</v>
+        <v>12050</v>
       </c>
       <c r="L6" t="n">
-        <v>7730</v>
+        <v>14550</v>
       </c>
       <c r="M6" t="n">
-        <v>6140</v>
+        <v>11950</v>
       </c>
       <c r="N6" t="n">
-        <v>7.35</v>
+        <v>5.42</v>
       </c>
       <c r="O6" t="n">
-        <v>66453785590</v>
+        <v>446002878090</v>
       </c>
       <c r="P6" t="n">
-        <v>21500</v>
+        <v>30200</v>
       </c>
       <c r="Q6" t="n">
-        <v>4565</v>
+        <v>3540</v>
       </c>
       <c r="R6" t="n">
-        <v>-376000</v>
+        <v>294000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>73000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>뎅기열 및 췌장암 치료제 관련 임상 결과 발표 기대감과 페니트리움바이오와의 시너지에 대한 긍정적 전망. 공매도 세력에 대한 경계도 있으나, 긍정적 데이터 공개 시 주가 상승 기대.</t>
+          <t>하반기 주도주로서 원전 및 로봇 섹터 전망. 미국 및 사우디 등 해외 수주 기대감 반영. 13750원 및 22300원 등 단기 목표가 제시. 정부 정책 및 외국인 자본 유입 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['뎅기열', '췌장암 치료제', '페니트리움바이오']</t>
+          <t>['원전', '로봇', '해외수주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>048410</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>현대바이오</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>54100</v>
+        <v>7150</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+9.85%</t>
+          <t>+14.22%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="F7" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G7" t="n">
-        <v>477</v>
+        <v>1035</v>
       </c>
       <c r="H7" t="n">
-        <v>14.96</v>
+        <v>7.4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>49250</v>
+        <v>6260</v>
       </c>
       <c r="K7" t="n">
-        <v>53500</v>
+        <v>6200</v>
       </c>
       <c r="L7" t="n">
-        <v>59000</v>
+        <v>7730</v>
       </c>
       <c r="M7" t="n">
-        <v>51600</v>
+        <v>6140</v>
       </c>
       <c r="N7" t="n">
-        <v>14.93</v>
+        <v>7.35</v>
       </c>
       <c r="O7" t="n">
-        <v>152740090550</v>
+        <v>67325430180</v>
       </c>
       <c r="P7" t="n">
-        <v>108900</v>
+        <v>21500</v>
       </c>
       <c r="Q7" t="n">
-        <v>18230</v>
+        <v>4565</v>
       </c>
       <c r="R7" t="n">
-        <v>-225000</v>
+        <v>-509000</v>
       </c>
       <c r="S7" t="n">
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2분기 영업이익 적자 기록 및 목표가 상향 조정 기대감 혼재.</t>
+          <t>췌장암 치료제 관련 임상 결과 발표 기대. 공매도와의 경쟁 및 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['영업이익', '목표가']</t>
+          <t>['췌장암 치료제', '임상 결과', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>048410</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14850</v>
+        <v>54200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.39%</t>
+          <t>+10.05%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.39</v>
+        <v>0.03</v>
       </c>
       <c r="E8" t="n">
-        <v>233</v>
+        <v>144</v>
       </c>
       <c r="F8" t="n">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="G8" t="n">
-        <v>1204</v>
+        <v>494</v>
       </c>
       <c r="H8" t="n">
-        <v>1.55</v>
+        <v>14.96</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>13700</v>
+        <v>49250</v>
       </c>
       <c r="K8" t="n">
-        <v>14260</v>
+        <v>53500</v>
       </c>
       <c r="L8" t="n">
-        <v>15860</v>
+        <v>59000</v>
       </c>
       <c r="M8" t="n">
-        <v>14210</v>
+        <v>51600</v>
       </c>
       <c r="N8" t="n">
-        <v>1.94</v>
+        <v>14.93</v>
       </c>
       <c r="O8" t="n">
-        <v>407205990290</v>
+        <v>154490394300</v>
       </c>
       <c r="P8" t="n">
-        <v>31500</v>
+        <v>108900</v>
       </c>
       <c r="Q8" t="n">
-        <v>1252</v>
+        <v>18230</v>
       </c>
       <c r="R8" t="n">
-        <v>820000</v>
+        <v>-220000</v>
       </c>
       <c r="S8" t="n">
-        <v>20000</v>
+        <v>135000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>빛과전자와의 시너지 기대감 속 거래대금 1위 기록. 단기 박스권 돌파.</t>
+          <t>두산퓨얼셀 수주 관련 긍정적 언급 및 목표가 상향 주장. 2분기 영업이익 적자에도 불구하고 향후 매출 성장성 기대. 기관 연기금 유입 및 공매도 세력 관련 논쟁.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신', '거래대금', '박스권 돌파']</t>
+          <t>['수주', '목표가', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3815</v>
+        <v>14830</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+4.81%</t>
+          <t>+8.25%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.74</v>
+        <v>-0.39</v>
       </c>
       <c r="E9" t="n">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="F9" t="n">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="G9" t="n">
-        <v>460</v>
+        <v>1252</v>
       </c>
       <c r="H9" t="n">
-        <v>3.19</v>
+        <v>1.55</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>3640</v>
+        <v>13700</v>
       </c>
       <c r="K9" t="n">
-        <v>3750</v>
+        <v>14260</v>
       </c>
       <c r="L9" t="n">
-        <v>4460</v>
+        <v>15860</v>
       </c>
       <c r="M9" t="n">
-        <v>3680</v>
+        <v>14210</v>
       </c>
       <c r="N9" t="n">
-        <v>0.45</v>
+        <v>1.94</v>
       </c>
       <c r="O9" t="n">
-        <v>265588595766</v>
+        <v>411682688180</v>
       </c>
       <c r="P9" t="n">
-        <v>8100</v>
+        <v>31500</v>
       </c>
       <c r="Q9" t="n">
-        <v>592</v>
+        <v>1252</v>
       </c>
       <c r="R9" t="n">
-        <v>-348000</v>
+        <v>488000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 광통신 시장 급등에 따른 기대감, 글로벌 회사 공급 뉴스.</t>
+          <t>단기 박스권 돌파 및 상승 추세 전망. 차트 분석 기반 가격 상승 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '글로벌 공급']</t>
+          <t>['차트 분석', '상승 추세', '단기 박스권']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8030</v>
+        <v>6780</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.56%</t>
+          <t>+5.44%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.4</v>
+        <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>104</v>
+        <v>327</v>
       </c>
       <c r="F10" t="n">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="G10" t="n">
-        <v>300</v>
+        <v>462</v>
       </c>
       <c r="H10" t="n">
-        <v>1.81</v>
+        <v>16.71</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>7680</v>
+        <v>6430</v>
       </c>
       <c r="K10" t="n">
-        <v>7780</v>
+        <v>6400</v>
       </c>
       <c r="L10" t="n">
-        <v>9000</v>
+        <v>7470</v>
       </c>
       <c r="M10" t="n">
-        <v>7750</v>
+        <v>6250</v>
       </c>
       <c r="N10" t="n">
-        <v>0.41</v>
+        <v>16.4</v>
       </c>
       <c r="O10" t="n">
-        <v>110178001370</v>
+        <v>95982087090</v>
       </c>
       <c r="P10" t="n">
-        <v>10300</v>
+        <v>13000</v>
       </c>
       <c r="Q10" t="n">
-        <v>952</v>
+        <v>6030</v>
       </c>
       <c r="R10" t="n">
-        <v>-206000</v>
+        <v>-684000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>레미콘 파업 및 긍정적인 시장 흐름에 따른 상한가 기대감. 하지만 구체적인 근거는 부족.</t>
+          <t>배당 관련 언급 있으나 주가 하락 우려 및 공매도 관련 부정적 전망 혼재. 외인 순매수 전환 기대감도 일부 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['레미콘 파업', '상한가 기대', '지지선']</t>
+          <t>['배당', '공매도', '외인']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6720</v>
+        <v>3795</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.51%</t>
+          <t>+4.26%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.31</v>
+        <v>2.74</v>
       </c>
       <c r="E11" t="n">
-        <v>317</v>
+        <v>209</v>
       </c>
       <c r="F11" t="n">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="G11" t="n">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="H11" t="n">
-        <v>16.71</v>
+        <v>3.19</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>6430</v>
+        <v>3640</v>
       </c>
       <c r="K11" t="n">
-        <v>6400</v>
+        <v>3750</v>
       </c>
       <c r="L11" t="n">
-        <v>7470</v>
+        <v>4460</v>
       </c>
       <c r="M11" t="n">
-        <v>6250</v>
+        <v>3680</v>
       </c>
       <c r="N11" t="n">
-        <v>16.4</v>
+        <v>0.45</v>
       </c>
       <c r="O11" t="n">
-        <v>94723395380</v>
+        <v>267541700273</v>
       </c>
       <c r="P11" t="n">
-        <v>13000</v>
+        <v>8100</v>
       </c>
       <c r="Q11" t="n">
-        <v>6030</v>
+        <v>592</v>
       </c>
       <c r="R11" t="n">
-        <v>-554000</v>
+        <v>-816000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>배당금 지급에도 불구하고 주가 부진, 공매도 관련 언급과 함께 투자자들의 불확실성 혼재.</t>
+          <t>미국 광통신 섹터 급등 및 관련 수혜 기대. 재료 우수성 및 거래량 풍부함 언급. 6천원 이상 목표가 설정 및 국책사업 선정 가능성 제기. 투기과열 지정 우려도 존재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['배당', '공매도']</t>
+          <t>['광통신', '재료', '국책사업']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2005</v>
+        <v>30900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+4.32%</t>
+          <t>+3.87%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.1</v>
+        <v>0.08</v>
       </c>
       <c r="E12" t="n">
-        <v>108</v>
+        <v>615</v>
       </c>
       <c r="F12" t="n">
-        <v>45</v>
+        <v>231</v>
       </c>
       <c r="G12" t="n">
-        <v>246</v>
+        <v>821</v>
       </c>
       <c r="H12" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1922</v>
+        <v>29750</v>
       </c>
       <c r="K12" t="n">
-        <v>1920</v>
+        <v>31600</v>
       </c>
       <c r="L12" t="n">
-        <v>2165</v>
+        <v>34200</v>
       </c>
       <c r="M12" t="n">
-        <v>1862</v>
+        <v>28300</v>
       </c>
       <c r="N12" t="n">
-        <v>0.61</v>
+        <v>0.23</v>
       </c>
       <c r="O12" t="n">
-        <v>16308568259</v>
+        <v>438695175550</v>
       </c>
       <c r="P12" t="n">
-        <v>2930</v>
+        <v>39350</v>
       </c>
       <c r="Q12" t="n">
-        <v>910</v>
+        <v>8200</v>
       </c>
       <c r="R12" t="n">
-        <v>70000</v>
+        <v>-1000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>호남반도체 클러스터 대장으로서의 역할 부각 및 텐버거 기대감. 대주주 매도 공시 등 부정적 요인도 있으나, 물량 소화 후 상승 전망.</t>
+          <t>혈압계 관련 기술 유럽 진출 뉴스. 상장 초기 급등 후 조정 국면.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['호남반도체', '텐버거', '대주주 매도']</t>
+          <t>['혈압계', '유럽 진출', '기술']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30750</v>
+        <v>1995</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.36%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>594</v>
+        <v>106</v>
       </c>
       <c r="F13" t="n">
-        <v>227</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>789</v>
+        <v>251</v>
       </c>
       <c r="H13" t="n">
-        <v>0.31</v>
+        <v>0.51</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>29750</v>
+        <v>1922</v>
       </c>
       <c r="K13" t="n">
-        <v>31600</v>
+        <v>1920</v>
       </c>
       <c r="L13" t="n">
-        <v>34200</v>
+        <v>2165</v>
       </c>
       <c r="M13" t="n">
-        <v>28300</v>
+        <v>1862</v>
       </c>
       <c r="N13" t="n">
-        <v>0.23</v>
+        <v>0.61</v>
       </c>
       <c r="O13" t="n">
-        <v>408742722825</v>
+        <v>16439677578</v>
       </c>
       <c r="P13" t="n">
-        <v>39350</v>
+        <v>2930</v>
       </c>
       <c r="Q13" t="n">
-        <v>8200</v>
+        <v>910</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>106000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>세계 최초 혈압 반지에 대한 유럽 진출 뉴스 및 ESC 관련 속보로 인한 긍정적 전망. 다만, 상장폐지 우려 및 단기 급등에 대한 경계감도 혼재.</t>
+          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['혈압 반지', '유럽 진출', 'ESC']</t>
+          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1847000</v>
+        <v>7950</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.01%</t>
+          <t>+3.52%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.03</v>
+        <v>1.4</v>
       </c>
       <c r="E14" t="n">
-        <v>798</v>
+        <v>105</v>
       </c>
       <c r="F14" t="n">
-        <v>459</v>
+        <v>71</v>
       </c>
       <c r="G14" t="n">
-        <v>2146</v>
+        <v>311</v>
       </c>
       <c r="H14" t="n">
-        <v>50.66</v>
+        <v>1.81</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1793000</v>
+        <v>7680</v>
       </c>
       <c r="K14" t="n">
-        <v>1795000</v>
+        <v>7780</v>
       </c>
       <c r="L14" t="n">
-        <v>1883000</v>
+        <v>9000</v>
       </c>
       <c r="M14" t="n">
-        <v>1795000</v>
+        <v>7750</v>
       </c>
       <c r="N14" t="n">
-        <v>50.63</v>
+        <v>0.41</v>
       </c>
       <c r="O14" t="n">
-        <v>4351450306000</v>
+        <v>111498719895</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>10300</v>
       </c>
       <c r="Q14" t="n">
-        <v>277000</v>
+        <v>952</v>
       </c>
       <c r="R14" t="n">
-        <v>53000</v>
+        <v>-210000</v>
       </c>
       <c r="S14" t="n">
-        <v>37000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>외국인 및 기관 매수세 유입에 따른 상승 추세 기대감. 자사주 매입.</t>
+          <t>레미콘 파업 및 긍정적인 시장 흐름에 따른 상한가 기대감. 하지만 구체적인 근거는 부족.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['외국인', '기관', '자사주']</t>
+          <t>['레미콘 파업', '상한가 기대', '지지선']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>91900</v>
+        <v>1852000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+2.68%</t>
+          <t>+3.29%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E15" t="n">
-        <v>309</v>
+        <v>795</v>
       </c>
       <c r="F15" t="n">
-        <v>197</v>
+        <v>458</v>
       </c>
       <c r="G15" t="n">
-        <v>1615</v>
+        <v>1978</v>
       </c>
       <c r="H15" t="n">
-        <v>23.61</v>
+        <v>50.66</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>89500</v>
+        <v>1793000</v>
       </c>
       <c r="K15" t="n">
-        <v>92000</v>
+        <v>1795000</v>
       </c>
       <c r="L15" t="n">
-        <v>94400</v>
+        <v>1883000</v>
       </c>
       <c r="M15" t="n">
-        <v>91300</v>
+        <v>1795000</v>
       </c>
       <c r="N15" t="n">
-        <v>23.63</v>
+        <v>50.63</v>
       </c>
       <c r="O15" t="n">
-        <v>266093131300</v>
+        <v>4628215964000</v>
       </c>
       <c r="P15" t="n">
-        <v>139200</v>
+        <v>2987000</v>
       </c>
       <c r="Q15" t="n">
-        <v>57000</v>
+        <v>277000</v>
       </c>
       <c r="R15" t="n">
-        <v>104000</v>
+        <v>157000</v>
       </c>
       <c r="S15" t="n">
-        <v>26000</v>
+        <v>153000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 원전 사업 참여 및 SMR 기술 관련 기대감. 프랑스와의 원자력 협력 뉴스 기반 상승 전망.</t>
+          <t>외국인 4일째 매수 중이며 수급 긍정적. 리밸런싱 완료 후 상승 추세 기대. 190 이상 돌파 및 두 자릿수 상승 가능성 언급. 단기 물량 이탈 확인.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '프랑스 협력']</t>
+          <t>['외국인', '수급', '상승추세']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12250</v>
+        <v>92000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>+2.79%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-2.16</v>
+        <v>-0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>164</v>
+        <v>311</v>
       </c>
       <c r="F16" t="n">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>315</v>
+        <v>1582</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>23.61</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>11990</v>
+        <v>89500</v>
       </c>
       <c r="K16" t="n">
-        <v>12440</v>
+        <v>92000</v>
       </c>
       <c r="L16" t="n">
-        <v>12800</v>
+        <v>94400</v>
       </c>
       <c r="M16" t="n">
-        <v>11920</v>
+        <v>91300</v>
       </c>
       <c r="N16" t="n">
-        <v>2.16</v>
+        <v>23.63</v>
       </c>
       <c r="O16" t="n">
-        <v>40878536410</v>
+        <v>273691831950</v>
       </c>
       <c r="P16" t="n">
-        <v>36200</v>
+        <v>139200</v>
       </c>
       <c r="Q16" t="n">
-        <v>8920</v>
+        <v>57000</v>
       </c>
       <c r="R16" t="n">
-        <v>43000</v>
+        <v>103000</v>
       </c>
       <c r="S16" t="n">
-        <v>-6000</v>
+        <v>66000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>국제유가 급등에 따른 기대감 고조. 지정학적 리스크 부각되며 유가 추가 상승 및 주가 상승 전망.</t>
+          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['국제유가', '지정학적 리스크']</t>
+          <t>['원전', 'SMR', '한-프랑스']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,86 +1936,86 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8990</v>
+        <v>12210</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>+1.83%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.36</v>
+        <v>-2.16</v>
       </c>
       <c r="E17" t="n">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="F17" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="G17" t="n">
-        <v>422</v>
+        <v>313</v>
       </c>
       <c r="H17" t="n">
-        <v>27.69</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8940</v>
+        <v>11990</v>
       </c>
       <c r="K17" t="n">
-        <v>8940</v>
+        <v>12440</v>
       </c>
       <c r="L17" t="n">
-        <v>9070</v>
+        <v>12800</v>
       </c>
       <c r="M17" t="n">
-        <v>8710</v>
+        <v>11920</v>
       </c>
       <c r="N17" t="n">
-        <v>28.05</v>
+        <v>2.16</v>
       </c>
       <c r="O17" t="n">
-        <v>25159938545</v>
+        <v>42373946165</v>
       </c>
       <c r="P17" t="n">
-        <v>17950</v>
+        <v>36200</v>
       </c>
       <c r="Q17" t="n">
-        <v>8120</v>
+        <v>8920</v>
       </c>
       <c r="R17" t="n">
-        <v>-289000</v>
+        <v>27000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>AI 문명 관련 기대감에도 불구하고 중국산 경쟁 심화 및 실적 부진으로 인한 주가 하락세 지속. 유상증자 및 시가총액 하락에 대한 부정적 전망 우세.</t>
+          <t>국제유가 급등에 따른 기대감 고조. 지정학적 리스크 부각되며 유가 추가 상승 및 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['AI', '중국산', '유상증자']</t>
+          <t>['국제유가', '지정학적 리스크']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>269750</v>
+        <v>8970</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.06</v>
+        <v>-0.36</v>
       </c>
       <c r="E18" t="n">
-        <v>793</v>
+        <v>105</v>
       </c>
       <c r="F18" t="n">
-        <v>471</v>
+        <v>64</v>
       </c>
       <c r="G18" t="n">
-        <v>1532</v>
+        <v>444</v>
       </c>
       <c r="H18" t="n">
-        <v>46.85</v>
+        <v>27.69</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>269500</v>
+        <v>8940</v>
       </c>
       <c r="K18" t="n">
-        <v>269500</v>
+        <v>8940</v>
       </c>
       <c r="L18" t="n">
-        <v>275000</v>
+        <v>9070</v>
       </c>
       <c r="M18" t="n">
-        <v>268500</v>
+        <v>8710</v>
       </c>
       <c r="N18" t="n">
-        <v>46.79</v>
+        <v>28.05</v>
       </c>
       <c r="O18" t="n">
-        <v>2844409840000</v>
+        <v>26673444165</v>
       </c>
       <c r="P18" t="n">
-        <v>374500</v>
+        <v>17950</v>
       </c>
       <c r="Q18" t="n">
-        <v>70000</v>
+        <v>8120</v>
       </c>
       <c r="R18" t="n">
-        <v>-301000</v>
+        <v>-481000</v>
       </c>
       <c r="S18" t="n">
-        <v>176000</v>
+        <v>5000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>SK하이닉스 등 경쟁사 대비 부진한 흐름에 대한 아쉬움 표출.</t>
+          <t>중국산 제품 경쟁력 및 부정적 전망. 주주 불만 및 기업의 낮은 주가 관리 능력 지적. AI 관련 언급은 있으나 구체적 호재는 부재.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['반도체', '경쟁사']</t>
+          <t>['중국산', '주가관리', 'AI']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19850</v>
+        <v>270000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.38</v>
+        <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>205</v>
+        <v>792</v>
       </c>
       <c r="F19" t="n">
-        <v>113</v>
+        <v>473</v>
       </c>
       <c r="G19" t="n">
-        <v>698</v>
+        <v>1553</v>
       </c>
       <c r="H19" t="n">
-        <v>10.85</v>
+        <v>46.85</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>19970</v>
+        <v>269500</v>
       </c>
       <c r="K19" t="n">
-        <v>20250</v>
+        <v>269500</v>
       </c>
       <c r="L19" t="n">
-        <v>21300</v>
+        <v>275000</v>
       </c>
       <c r="M19" t="n">
-        <v>19630</v>
+        <v>268500</v>
       </c>
       <c r="N19" t="n">
-        <v>10.47</v>
+        <v>46.79</v>
       </c>
       <c r="O19" t="n">
-        <v>236289758345</v>
+        <v>3027345347500</v>
       </c>
       <c r="P19" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q19" t="n">
-        <v>3320</v>
+        <v>70000</v>
       </c>
       <c r="R19" t="n">
-        <v>-844000</v>
+        <v>-1252000</v>
       </c>
       <c r="S19" t="n">
-        <v>45000</v>
+        <v>720000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 원전 사업 참여 기대감 속 계약 체결 공시 확인.</t>
+          <t>SK하이닉스와의 주가 상승률 비교 및 상대적 부진에 대한 지적. 외국인 선물 매도 전환 등 부정적 신호 감지. 자사주 매입 요구 및 목표가 상향 의견도 일부.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', '계약 체결']</t>
+          <t>['반도체', '외국인', '목표가']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33850</v>
+        <v>33800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F20" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G20" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="H20" t="n">
         <v>52.59</v>
@@ -2260,13 +2260,13 @@
         <v>35325</v>
       </c>
       <c r="M20" t="n">
-        <v>33800</v>
+        <v>33750</v>
       </c>
       <c r="N20" t="n">
         <v>21.01</v>
       </c>
       <c r="O20" t="n">
-        <v>67924412150</v>
+        <v>70947402525</v>
       </c>
       <c r="P20" t="n">
         <v>69500</v>
@@ -2275,14 +2275,14 @@
         <v>30400</v>
       </c>
       <c r="R20" t="n">
-        <v>-78000</v>
+        <v>-69000</v>
       </c>
       <c r="S20" t="n">
-        <v>61000</v>
+        <v>68000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 원전 협력 강화 및 차세대 원전 사업 관련 긍정적 전망. 전기료 인상 및 발전 5사 통합 논의도 주가에 영향을 미칠 가능성. 다만, 공매도 및 정부 기업의 한계성에 대한 우려도 존재.</t>
+          <t>미국 원전 협력 및 한국-프랑스 차세대 원전 사업 기대. 발전 5사 통합 및 선납매 이슈.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전 협력', '전기료 인상', '발전 5사 통합']</t>
+          <t>['원전', '미국 협력', '발전 5사']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2311,31 +2311,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10230</v>
+        <v>19790</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.01%</t>
+          <t>-0.90%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="E21" t="n">
-        <v>98</v>
+        <v>209</v>
       </c>
       <c r="F21" t="n">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="G21" t="n">
-        <v>200</v>
+        <v>699</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9399999999999999</v>
+        <v>10.85</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>10440</v>
+        <v>19970</v>
       </c>
       <c r="K21" t="n">
-        <v>10180</v>
+        <v>20250</v>
       </c>
       <c r="L21" t="n">
-        <v>11340</v>
+        <v>21300</v>
       </c>
       <c r="M21" t="n">
-        <v>9980</v>
+        <v>19630</v>
       </c>
       <c r="N21" t="n">
-        <v>0.62</v>
+        <v>10.47</v>
       </c>
       <c r="O21" t="n">
-        <v>141662149515</v>
+        <v>242991349215</v>
       </c>
       <c r="P21" t="n">
-        <v>15960</v>
+        <v>40350</v>
       </c>
       <c r="Q21" t="n">
-        <v>3500</v>
+        <v>3320</v>
       </c>
       <c r="R21" t="n">
-        <v>-43000</v>
+        <v>-1134000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-151000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 제약바이오 시장 혼조세 속 탈모주 관련 기대감.</t>
+          <t>미국 원전 사업 참여 기대감 속 계약 체결 공시 확인.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['탈모주', '신고가']</t>
+          <t>['원전', '계약 체결']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,97 +2396,189 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3765</v>
+        <v>10120</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.21%</t>
+          <t>-3.07%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.52</v>
+        <v>0.32</v>
       </c>
       <c r="E22" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F22" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="G22" t="n">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="H22" t="n">
-        <v>2.08</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>3890</v>
+        <v>10440</v>
       </c>
       <c r="K22" t="n">
-        <v>3890</v>
+        <v>10180</v>
       </c>
       <c r="L22" t="n">
-        <v>4115</v>
+        <v>11340</v>
       </c>
       <c r="M22" t="n">
-        <v>3700</v>
+        <v>9980</v>
       </c>
       <c r="N22" t="n">
-        <v>1.56</v>
+        <v>0.62</v>
       </c>
       <c r="O22" t="n">
-        <v>63311995606</v>
+        <v>143263719045</v>
       </c>
       <c r="P22" t="n">
-        <v>4335</v>
+        <v>15960</v>
       </c>
       <c r="Q22" t="n">
-        <v>1246</v>
+        <v>3500</v>
       </c>
       <c r="R22" t="n">
-        <v>-505000</v>
+        <v>-11000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>탈모 관련 기대감과 조정·하락 우려 공존. 재료 부족 논란.</t>
+          <t>미국 제약 바이오 시장 동향 언급 및 주포 관련 부정적 의견 존재. 탈모 관련 테마 기대감 및 신고가 돌파 의지 표출.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>['탈모주', '신고가', '주포']</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>004310</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>JW신약</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3735</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-3.98%</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E23" t="n">
+        <v>94</v>
+      </c>
+      <c r="F23" t="n">
+        <v>50</v>
+      </c>
+      <c r="G23" t="n">
+        <v>181</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>3890</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3890</v>
+      </c>
+      <c r="L23" t="n">
+        <v>4115</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3700</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O23" t="n">
+        <v>64364158194</v>
+      </c>
+      <c r="P23" t="n">
+        <v>4335</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1246</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-519000</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>탈모 관련 제약주 수급 변화 가능성 언급. 일부 하락 및 보합세 전망.</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
         <v>0.1</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>['탈모', '조정', '재료']</t>
-        </is>
-      </c>
-      <c r="X22" t="n">
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>['탈모 치료제', '제약주', '수급']</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
         <v>8</v>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>067290</t>
         </is>

--- a/data/trending_integrated_20260909_13.xlsx
+++ b/data/trending_integrated_20260909_13.xlsx
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F2" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G2" t="n">
-        <v>1346</v>
+        <v>1377</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29638325495</v>
+        <v>29644016635</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -670,13 +670,13 @@
         <v>0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G3" t="n">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="H3" t="n">
         <v>2.46</v>
@@ -702,7 +702,7 @@
         <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>37761774195</v>
+        <v>37785222525</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2640</v>
+        <v>2645</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+22.22%</t>
+          <t>+22.45%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="H4" t="n">
         <v>5.26</v>
@@ -785,7 +785,7 @@
         <v>2200</v>
       </c>
       <c r="L4" t="n">
-        <v>2670</v>
+        <v>2700</v>
       </c>
       <c r="M4" t="n">
         <v>2200</v>
@@ -794,10 +794,10 @@
         <v>5.49</v>
       </c>
       <c r="O4" t="n">
-        <v>27353186547</v>
+        <v>29777779299</v>
       </c>
       <c r="P4" t="n">
-        <v>2670</v>
+        <v>2700</v>
       </c>
       <c r="Q4" t="n">
         <v>1418</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>경영권 분쟁 및 신규 대주주 관련 긍정적 전망. 단기 급등 기대감 및 기타법인 매수세 유입 관찰. 과열 우려 및 매도량 급증 주의.</t>
+          <t>경영권 분쟁 및 지분 싸움 가능성, 엔비디아 관련 루머 및 단기 과열 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['경영권분쟁', '기타법인', '단기과열']</t>
+          <t>['지분싸움', '엔비디아', '경영권']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12210</v>
+        <v>12160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+21.73%</t>
+          <t>+21.24%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F5" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G5" t="n">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="H5" t="n">
         <v>0.36</v>
@@ -886,7 +886,7 @@
         <v>0.44</v>
       </c>
       <c r="O5" t="n">
-        <v>184430443710</v>
+        <v>186908591250</v>
       </c>
       <c r="P5" t="n">
         <v>20850</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>가스터빈 및 원전 관련 사업 부각. 국내 1위 업체로 미국 시장 진출 기대.</t>
+          <t>SMR 및 가스터빈 관련 사업 부각, 미국 발전소 투자 확대 뉴스 기반 상승 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['가스터빈', '원전', '미국 시장']</t>
+          <t>['SMR', '가스터빈', '미국투자']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13870</v>
+        <v>13940</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+17.44%</t>
+          <t>+18.04%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.22</v>
       </c>
       <c r="E6" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F6" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G6" t="n">
-        <v>1252</v>
+        <v>1276</v>
       </c>
       <c r="H6" t="n">
         <v>5.64</v>
@@ -978,7 +978,7 @@
         <v>5.42</v>
       </c>
       <c r="O6" t="n">
-        <v>446002878090</v>
+        <v>452028611710</v>
       </c>
       <c r="P6" t="n">
         <v>30200</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7150</v>
+        <v>7140</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+14.22%</t>
+          <t>+14.06%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F7" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G7" t="n">
-        <v>1035</v>
+        <v>1069</v>
       </c>
       <c r="H7" t="n">
         <v>7.4</v>
@@ -1070,7 +1070,7 @@
         <v>7.35</v>
       </c>
       <c r="O7" t="n">
-        <v>67325430180</v>
+        <v>67567685965</v>
       </c>
       <c r="P7" t="n">
         <v>21500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>췌장암 치료제 관련 임상 결과 발표 기대. 공매도와의 경쟁 및 주가 상승 전망.</t>
+          <t>뎅기열 중간 발표 기대감과 페니트리움바이오 관련 임상 데이터 발표 예정. 공매도와의 경쟁 속 거래량 증가 추세.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['췌장암 치료제', '임상 결과', '공매도']</t>
+          <t>['뎅기열', '페니트리움', '임상 데이터']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54200</v>
+        <v>54100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+10.05%</t>
+          <t>+9.85%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.03</v>
       </c>
       <c r="E8" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F8" t="n">
         <v>113</v>
       </c>
       <c r="G8" t="n">
-        <v>494</v>
+        <v>530</v>
       </c>
       <c r="H8" t="n">
         <v>14.96</v>
@@ -1162,7 +1162,7 @@
         <v>14.93</v>
       </c>
       <c r="O8" t="n">
-        <v>154490394300</v>
+        <v>155416736150</v>
       </c>
       <c r="P8" t="n">
         <v>108900</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>두산퓨얼셀 수주 관련 긍정적 언급 및 목표가 상향 주장. 2분기 영업이익 적자에도 불구하고 향후 매출 성장성 기대. 기관 연기금 유입 및 공매도 세력 관련 논쟁.</t>
+          <t>수주 관련 언급 및 2분기 실적 부진, 목표가 상향 전망 및 기관 연기금 매수 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수주', '목표가', '공매도']</t>
+          <t>['수주', '실적', '목표가']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14830</v>
+        <v>14880</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+8.25%</t>
+          <t>+8.61%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.39</v>
       </c>
       <c r="E9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F9" t="n">
         <v>146</v>
       </c>
       <c r="G9" t="n">
-        <v>1252</v>
+        <v>1276</v>
       </c>
       <c r="H9" t="n">
         <v>1.55</v>
@@ -1254,7 +1254,7 @@
         <v>1.94</v>
       </c>
       <c r="O9" t="n">
-        <v>411682688180</v>
+        <v>413754855825</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6780</v>
+        <v>6790</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.44%</t>
+          <t>+5.60%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>327</v>
+        <v>158</v>
       </c>
       <c r="F10" t="n">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="G10" t="n">
-        <v>462</v>
+        <v>286</v>
       </c>
       <c r="H10" t="n">
         <v>16.71</v>
@@ -1346,7 +1346,7 @@
         <v>16.4</v>
       </c>
       <c r="O10" t="n">
-        <v>95982087090</v>
+        <v>96405403020</v>
       </c>
       <c r="P10" t="n">
         <v>13000</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>배당 관련 언급 있으나 주가 하락 우려 및 공매도 관련 부정적 전망 혼재. 외인 순매수 전환 기대감도 일부 존재.</t>
+          <t>배당 관련 언급은 있으나 주가 부양에 대한 구체적인 근거 부족, 외인 유입 여부 불확실.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['배당', '공매도', '외인']</t>
+          <t>['배당', '외인']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3795</v>
+        <v>31050</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.26%</t>
+          <t>+4.37%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.74</v>
+        <v>0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>209</v>
+        <v>625</v>
       </c>
       <c r="F11" t="n">
-        <v>121</v>
+        <v>232</v>
       </c>
       <c r="G11" t="n">
-        <v>471</v>
+        <v>846</v>
       </c>
       <c r="H11" t="n">
-        <v>3.19</v>
+        <v>0.31</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3640</v>
+        <v>29750</v>
       </c>
       <c r="K11" t="n">
-        <v>3750</v>
+        <v>31600</v>
       </c>
       <c r="L11" t="n">
-        <v>4460</v>
+        <v>34200</v>
       </c>
       <c r="M11" t="n">
-        <v>3680</v>
+        <v>28300</v>
       </c>
       <c r="N11" t="n">
-        <v>0.45</v>
+        <v>0.23</v>
       </c>
       <c r="O11" t="n">
-        <v>267541700273</v>
+        <v>446292048850</v>
       </c>
       <c r="P11" t="n">
-        <v>8100</v>
+        <v>39350</v>
       </c>
       <c r="Q11" t="n">
-        <v>592</v>
+        <v>8200</v>
       </c>
       <c r="R11" t="n">
-        <v>-816000</v>
+        <v>-1000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 급등 및 관련 수혜 기대. 재료 우수성 및 거래량 풍부함 언급. 6천원 이상 목표가 설정 및 국책사업 선정 가능성 제기. 투기과열 지정 우려도 존재.</t>
+          <t>혈압계 관련 기술 유럽 진출 뉴스. 상장 초기 급등 후 조정 국면.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '재료', '국책사업']</t>
+          <t>['혈압계', '유럽 진출', '기술']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30900</v>
+        <v>8010</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.87%</t>
+          <t>+4.30%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.08</v>
+        <v>1.4</v>
       </c>
       <c r="E12" t="n">
-        <v>615</v>
+        <v>107</v>
       </c>
       <c r="F12" t="n">
-        <v>231</v>
+        <v>71</v>
       </c>
       <c r="G12" t="n">
-        <v>821</v>
+        <v>315</v>
       </c>
       <c r="H12" t="n">
-        <v>0.31</v>
+        <v>1.81</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>29750</v>
+        <v>7680</v>
       </c>
       <c r="K12" t="n">
-        <v>31600</v>
+        <v>7780</v>
       </c>
       <c r="L12" t="n">
-        <v>34200</v>
+        <v>9000</v>
       </c>
       <c r="M12" t="n">
-        <v>28300</v>
+        <v>7750</v>
       </c>
       <c r="N12" t="n">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="O12" t="n">
-        <v>438695175550</v>
+        <v>111870587010</v>
       </c>
       <c r="P12" t="n">
-        <v>39350</v>
+        <v>10300</v>
       </c>
       <c r="Q12" t="n">
-        <v>8200</v>
+        <v>952</v>
       </c>
       <c r="R12" t="n">
-        <v>-1000</v>
+        <v>-210000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>혈압계 관련 기술 유럽 진출 뉴스. 상장 초기 급등 후 조정 국면.</t>
+          <t>레미콘 파업 관련 기대감 및 강한 지지선 언급, 당일 상승 추세.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['혈압계', '유럽 진출', '기술']</t>
+          <t>['레미콘', '파업', '지지선']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1995</v>
+        <v>3792</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.80%</t>
+          <t>+4.18%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1</v>
+        <v>2.74</v>
       </c>
       <c r="E13" t="n">
-        <v>106</v>
+        <v>213</v>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>122</v>
       </c>
       <c r="G13" t="n">
-        <v>251</v>
+        <v>480</v>
       </c>
       <c r="H13" t="n">
-        <v>0.51</v>
+        <v>3.19</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,47 +1607,47 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1922</v>
+        <v>3640</v>
       </c>
       <c r="K13" t="n">
-        <v>1920</v>
+        <v>3750</v>
       </c>
       <c r="L13" t="n">
-        <v>2165</v>
+        <v>4460</v>
       </c>
       <c r="M13" t="n">
-        <v>1862</v>
+        <v>3680</v>
       </c>
       <c r="N13" t="n">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="O13" t="n">
-        <v>16439677578</v>
+        <v>268457392846</v>
       </c>
       <c r="P13" t="n">
-        <v>2930</v>
+        <v>8100</v>
       </c>
       <c r="Q13" t="n">
-        <v>910</v>
+        <v>592</v>
       </c>
       <c r="R13" t="n">
-        <v>106000</v>
+        <v>-816000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
+          <t>미국 광통신 섹터 급등 및 관련 수혜 기대. 재료 우수성 및 거래량 풍부함 언급. 6천원 이상 목표가 설정 및 국책사업 선정 가능성 제기. 투기과열 지정 우려도 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
+          <t>['광통신', '재료', '국책사업']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7950</v>
+        <v>1863000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.52%</t>
+          <t>+3.90%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.4</v>
+        <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>105</v>
+        <v>798</v>
       </c>
       <c r="F14" t="n">
-        <v>71</v>
+        <v>456</v>
       </c>
       <c r="G14" t="n">
-        <v>311</v>
+        <v>1873</v>
       </c>
       <c r="H14" t="n">
-        <v>1.81</v>
+        <v>50.66</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7680</v>
+        <v>1793000</v>
       </c>
       <c r="K14" t="n">
-        <v>7780</v>
+        <v>1795000</v>
       </c>
       <c r="L14" t="n">
-        <v>9000</v>
+        <v>1883000</v>
       </c>
       <c r="M14" t="n">
-        <v>7750</v>
+        <v>1795000</v>
       </c>
       <c r="N14" t="n">
-        <v>0.41</v>
+        <v>50.63</v>
       </c>
       <c r="O14" t="n">
-        <v>111498719895</v>
+        <v>4757133693000</v>
       </c>
       <c r="P14" t="n">
-        <v>10300</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>952</v>
+        <v>277000</v>
       </c>
       <c r="R14" t="n">
-        <v>-210000</v>
+        <v>157000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>153000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>레미콘 파업 및 긍정적인 시장 흐름에 따른 상한가 기대감. 하지만 구체적인 근거는 부족.</t>
+          <t>외인 4일째 매수 중, 호가창 가벼워짐 및 상승 추세 기대감, 전일 대비 분위기 변화.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['레미콘 파업', '상한가 기대', '지지선']</t>
+          <t>['외인매수', '상승추세']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1852000</v>
+        <v>1995</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.29%</t>
+          <t>+3.80%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="E15" t="n">
-        <v>795</v>
+        <v>109</v>
       </c>
       <c r="F15" t="n">
-        <v>458</v>
+        <v>44</v>
       </c>
       <c r="G15" t="n">
-        <v>1978</v>
+        <v>254</v>
       </c>
       <c r="H15" t="n">
-        <v>50.66</v>
+        <v>0.51</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1793000</v>
+        <v>1922</v>
       </c>
       <c r="K15" t="n">
-        <v>1795000</v>
+        <v>1920</v>
       </c>
       <c r="L15" t="n">
-        <v>1883000</v>
+        <v>2165</v>
       </c>
       <c r="M15" t="n">
-        <v>1795000</v>
+        <v>1862</v>
       </c>
       <c r="N15" t="n">
-        <v>50.63</v>
+        <v>0.61</v>
       </c>
       <c r="O15" t="n">
-        <v>4628215964000</v>
+        <v>16506600266</v>
       </c>
       <c r="P15" t="n">
-        <v>2987000</v>
+        <v>2930</v>
       </c>
       <c r="Q15" t="n">
-        <v>277000</v>
+        <v>910</v>
       </c>
       <c r="R15" t="n">
-        <v>157000</v>
+        <v>106000</v>
       </c>
       <c r="S15" t="n">
-        <v>153000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>외국인 4일째 매수 중이며 수급 긍정적. 리밸런싱 완료 후 상승 추세 기대. 190 이상 돌파 및 두 자릿수 상승 가능성 언급. 단기 물량 이탈 확인.</t>
+          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['외국인', '수급', '상승추세']</t>
+          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
@@ -1866,13 +1866,13 @@
         <v>-0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="F16" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G16" t="n">
-        <v>1582</v>
+        <v>1605</v>
       </c>
       <c r="H16" t="n">
         <v>23.61</v>
@@ -1898,7 +1898,7 @@
         <v>23.63</v>
       </c>
       <c r="O16" t="n">
-        <v>273691831950</v>
+        <v>276414420150</v>
       </c>
       <c r="P16" t="n">
         <v>139200</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12210</v>
+        <v>12070</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+1.83%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-2.16</v>
       </c>
       <c r="E17" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F17" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G17" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
         <v>2.16</v>
       </c>
       <c r="O17" t="n">
-        <v>42373946165</v>
+        <v>43330055710</v>
       </c>
       <c r="P17" t="n">
         <v>36200</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8970</v>
+        <v>8990</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.36</v>
       </c>
       <c r="E18" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F18" t="n">
         <v>64</v>
       </c>
       <c r="G18" t="n">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="H18" t="n">
         <v>27.69</v>
@@ -2082,7 +2082,7 @@
         <v>28.05</v>
       </c>
       <c r="O18" t="n">
-        <v>26673444165</v>
+        <v>27340992090</v>
       </c>
       <c r="P18" t="n">
         <v>17950</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>270000</v>
+        <v>270750</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>792</v>
+        <v>654</v>
       </c>
       <c r="F19" t="n">
-        <v>473</v>
+        <v>409</v>
       </c>
       <c r="G19" t="n">
-        <v>1553</v>
+        <v>1229</v>
       </c>
       <c r="H19" t="n">
         <v>46.85</v>
@@ -2174,7 +2174,7 @@
         <v>46.79</v>
       </c>
       <c r="O19" t="n">
-        <v>3027345347500</v>
+        <v>3101435211000</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>SK하이닉스와의 주가 상승률 비교 및 상대적 부진에 대한 지적. 외국인 선물 매도 전환 등 부정적 신호 감지. 자사주 매입 요구 및 목표가 상향 의견도 일부.</t>
+          <t>SK하이닉스 대비 부진한 주가 흐름, 자사주 매입 및 주가 부양 기대감 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['반도체', '외국인', '목표가']</t>
+          <t>['SK하이닉스', '자사주매입']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2219,31 +2219,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33800</v>
+        <v>19850</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="E20" t="n">
-        <v>113</v>
+        <v>160</v>
       </c>
       <c r="F20" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="G20" t="n">
-        <v>263</v>
+        <v>437</v>
       </c>
       <c r="H20" t="n">
-        <v>52.59</v>
+        <v>10.85</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,38 +2251,38 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>34100</v>
+        <v>19970</v>
       </c>
       <c r="K20" t="n">
-        <v>34450</v>
+        <v>20250</v>
       </c>
       <c r="L20" t="n">
-        <v>35325</v>
+        <v>21300</v>
       </c>
       <c r="M20" t="n">
-        <v>33750</v>
+        <v>19630</v>
       </c>
       <c r="N20" t="n">
-        <v>21.01</v>
+        <v>10.47</v>
       </c>
       <c r="O20" t="n">
-        <v>70947402525</v>
+        <v>245308735610</v>
       </c>
       <c r="P20" t="n">
-        <v>69500</v>
+        <v>40350</v>
       </c>
       <c r="Q20" t="n">
-        <v>30400</v>
+        <v>3320</v>
       </c>
       <c r="R20" t="n">
-        <v>-69000</v>
+        <v>-1134000</v>
       </c>
       <c r="S20" t="n">
-        <v>68000</v>
+        <v>-151000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 원전 협력 및 한국-프랑스 차세대 원전 사업 기대. 발전 5사 통합 및 선납매 이슈.</t>
+          <t>계약 체결 공시 확인, 공매도 관련 언급 있으나 차트상 긍정적 전망.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전', '미국 협력', '발전 5사']</t>
+          <t>['공시', '계약체결', '공매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19790</v>
+        <v>33850</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.90%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.38</v>
+        <v>0.1</v>
       </c>
       <c r="E21" t="n">
-        <v>209</v>
+        <v>119</v>
       </c>
       <c r="F21" t="n">
-        <v>114</v>
+        <v>59</v>
       </c>
       <c r="G21" t="n">
-        <v>699</v>
+        <v>271</v>
       </c>
       <c r="H21" t="n">
-        <v>10.85</v>
+        <v>52.59</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>19970</v>
+        <v>34100</v>
       </c>
       <c r="K21" t="n">
-        <v>20250</v>
+        <v>34450</v>
       </c>
       <c r="L21" t="n">
-        <v>21300</v>
+        <v>35325</v>
       </c>
       <c r="M21" t="n">
-        <v>19630</v>
+        <v>33750</v>
       </c>
       <c r="N21" t="n">
-        <v>10.47</v>
+        <v>21.01</v>
       </c>
       <c r="O21" t="n">
-        <v>242991349215</v>
+        <v>72345336125</v>
       </c>
       <c r="P21" t="n">
-        <v>40350</v>
+        <v>69500</v>
       </c>
       <c r="Q21" t="n">
-        <v>3320</v>
+        <v>30400</v>
       </c>
       <c r="R21" t="n">
-        <v>-1134000</v>
+        <v>-69000</v>
       </c>
       <c r="S21" t="n">
-        <v>-151000</v>
+        <v>68000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 원전 사업 참여 기대감 속 계약 체결 공시 확인.</t>
+          <t>미국 원전 협력 기대감과 25조 선납매 언급. SMP 급락 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '계약 체결']</t>
+          <t>['원전', '선납매', 'SMP']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>015760</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10120</v>
+        <v>10140</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>-2.87%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.32</v>
       </c>
       <c r="E22" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F22" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G22" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H22" t="n">
         <v>0.9399999999999999</v>
@@ -2450,7 +2450,7 @@
         <v>0.62</v>
       </c>
       <c r="O22" t="n">
-        <v>143263719045</v>
+        <v>144027634705</v>
       </c>
       <c r="P22" t="n">
         <v>15960</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>미국 제약 바이오 시장 동향 언급 및 주포 관련 부정적 의견 존재. 탈모 관련 테마 기대감 및 신고가 돌파 의지 표출.</t>
+          <t>미증시 제약바이오와는 다른 움직임, 탈모주 관련 기대감 있으나 구체적인 재료 및 공시 부재.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['탈모주', '신고가', '주포']</t>
+          <t>['탈모주', '재료']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3735</v>
+        <v>3755</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.98%</t>
+          <t>-3.47%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.52</v>
       </c>
       <c r="E23" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F23" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G23" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H23" t="n">
         <v>2.08</v>
@@ -2542,7 +2542,7 @@
         <v>1.56</v>
       </c>
       <c r="O23" t="n">
-        <v>64364158194</v>
+        <v>64634348454</v>
       </c>
       <c r="P23" t="n">
         <v>4335</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>탈모 관련 제약주 수급 변화 가능성 언급. 일부 하락 및 보합세 전망.</t>
+          <t>탈모 관련주로 언급되나 구체적인 재료 및 뉴스 부재, 하락 추세 및 조정 국면.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['탈모 치료제', '제약주', '수급']</t>
+          <t>['탈모주', '하락']</t>
         </is>
       </c>
       <c r="X23" t="n">
